--- a/artfynd/A 44305-2024 artfynd.xlsx
+++ b/artfynd/A 44305-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150451</v>
+        <v>121150453</v>
       </c>
       <c r="B2" t="n">
-        <v>78334</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758558</v>
+        <v>758420</v>
       </c>
       <c r="R2" t="n">
-        <v>7412036</v>
+        <v>7412020</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>121150454</v>
       </c>
       <c r="B3" t="n">
-        <v>90880</v>
+        <v>90890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150453</v>
+        <v>121150452</v>
       </c>
       <c r="B4" t="n">
-        <v>90683</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758420</v>
+        <v>758406</v>
       </c>
       <c r="R4" t="n">
-        <v>7412020</v>
+        <v>7411982</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150452</v>
+        <v>121150451</v>
       </c>
       <c r="B5" t="n">
-        <v>90683</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758406</v>
+        <v>758558</v>
       </c>
       <c r="R5" t="n">
-        <v>7411982</v>
+        <v>7412036</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44305-2024 artfynd.xlsx
+++ b/artfynd/A 44305-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150453</v>
+        <v>121150454</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>90890</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758420</v>
+        <v>758583</v>
       </c>
       <c r="R2" t="n">
-        <v>7412020</v>
+        <v>7411837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150454</v>
+        <v>121150451</v>
       </c>
       <c r="B3" t="n">
-        <v>90890</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758583</v>
+        <v>758558</v>
       </c>
       <c r="R3" t="n">
-        <v>7411837</v>
+        <v>7412036</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150451</v>
+        <v>121150453</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>90693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758558</v>
+        <v>758420</v>
       </c>
       <c r="R5" t="n">
-        <v>7412036</v>
+        <v>7412020</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44305-2024 artfynd.xlsx
+++ b/artfynd/A 44305-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150454</v>
+        <v>121150451</v>
       </c>
       <c r="B2" t="n">
-        <v>90890</v>
+        <v>78340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758583</v>
+        <v>758558</v>
       </c>
       <c r="R2" t="n">
-        <v>7411837</v>
+        <v>7412036</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150451</v>
+        <v>121150452</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>90705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758558</v>
+        <v>758406</v>
       </c>
       <c r="R3" t="n">
-        <v>7412036</v>
+        <v>7411982</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150452</v>
+        <v>121150453</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>90705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758406</v>
+        <v>758420</v>
       </c>
       <c r="R4" t="n">
-        <v>7411982</v>
+        <v>7412020</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150453</v>
+        <v>121150454</v>
       </c>
       <c r="B5" t="n">
-        <v>90693</v>
+        <v>90902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758420</v>
+        <v>758583</v>
       </c>
       <c r="R5" t="n">
-        <v>7412020</v>
+        <v>7411837</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44305-2024 artfynd.xlsx
+++ b/artfynd/A 44305-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150451</v>
+        <v>121150454</v>
       </c>
       <c r="B2" t="n">
-        <v>78340</v>
+        <v>90903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758558</v>
+        <v>758583</v>
       </c>
       <c r="R2" t="n">
-        <v>7412036</v>
+        <v>7411837</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150452</v>
+        <v>121150453</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>90706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758406</v>
+        <v>758420</v>
       </c>
       <c r="R3" t="n">
-        <v>7411982</v>
+        <v>7412020</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150453</v>
+        <v>121150451</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>78340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758420</v>
+        <v>758558</v>
       </c>
       <c r="R4" t="n">
-        <v>7412020</v>
+        <v>7412036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150454</v>
+        <v>121150452</v>
       </c>
       <c r="B5" t="n">
-        <v>90902</v>
+        <v>90706</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758583</v>
+        <v>758406</v>
       </c>
       <c r="R5" t="n">
-        <v>7411837</v>
+        <v>7411982</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44305-2024 artfynd.xlsx
+++ b/artfynd/A 44305-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150454</v>
+        <v>121150453</v>
       </c>
       <c r="B2" t="n">
-        <v>90903</v>
+        <v>90709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758583</v>
+        <v>758420</v>
       </c>
       <c r="R2" t="n">
-        <v>7411837</v>
+        <v>7412020</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150453</v>
+        <v>121150452</v>
       </c>
       <c r="B3" t="n">
-        <v>90706</v>
+        <v>90709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758420</v>
+        <v>758406</v>
       </c>
       <c r="R3" t="n">
-        <v>7412020</v>
+        <v>7411982</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150451</v>
+        <v>121150454</v>
       </c>
       <c r="B4" t="n">
-        <v>78340</v>
+        <v>90906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758558</v>
+        <v>758583</v>
       </c>
       <c r="R4" t="n">
-        <v>7412036</v>
+        <v>7411837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150452</v>
+        <v>121150451</v>
       </c>
       <c r="B5" t="n">
-        <v>90706</v>
+        <v>78343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758406</v>
+        <v>758558</v>
       </c>
       <c r="R5" t="n">
-        <v>7411982</v>
+        <v>7412036</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 44305-2024 artfynd.xlsx
+++ b/artfynd/A 44305-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150453</v>
+        <v>121150451</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>78343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758420</v>
+        <v>758558</v>
       </c>
       <c r="R2" t="n">
-        <v>7412020</v>
+        <v>7412036</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150452</v>
+        <v>121150454</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
+        <v>90906</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758406</v>
+        <v>758583</v>
       </c>
       <c r="R3" t="n">
-        <v>7411982</v>
+        <v>7411837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150454</v>
+        <v>121150453</v>
       </c>
       <c r="B4" t="n">
-        <v>90906</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758583</v>
+        <v>758420</v>
       </c>
       <c r="R4" t="n">
-        <v>7411837</v>
+        <v>7412020</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150451</v>
+        <v>121150452</v>
       </c>
       <c r="B5" t="n">
-        <v>78343</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758558</v>
+        <v>758406</v>
       </c>
       <c r="R5" t="n">
-        <v>7412036</v>
+        <v>7411982</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
